--- a/docs/build/lakeshore-enterprise-context/source/05_treasury_kyriba/bank_connectivity_inventory.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/05_treasury_kyriba/bank_connectivity_inventory.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EBICS</t>
+          <t>H2H</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -505,11 +505,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CAMT.053</t>
+          <t>BAI2</t>
         </is>
       </c>
     </row>
@@ -526,16 +526,16 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SWIFT</t>
+          <t>API</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -556,20 +556,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>H2H</t>
+          <t>API</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CAMT.053</t>
+          <t>MT942</t>
         </is>
       </c>
     </row>
@@ -586,16 +586,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>H2H</t>
+          <t>EBICS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -621,15 +621,15 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BAI2</t>
+          <t>MT942</t>
         </is>
       </c>
     </row>
@@ -646,16 +646,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>H2H</t>
+          <t>API</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -676,20 +676,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>EBICS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BAI2</t>
+          <t>MT942</t>
         </is>
       </c>
     </row>
@@ -706,20 +706,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SWIFT</t>
+          <t>API</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CAMT.053</t>
+          <t>BAI2</t>
         </is>
       </c>
     </row>
@@ -741,15 +741,15 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MT942</t>
+          <t>CAMT.053</t>
         </is>
       </c>
     </row>
@@ -766,16 +766,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SWIFT</t>
+          <t>API</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
